--- a/TUCUMAN 1061/Agosto/tucuman Agosto.xlsx
+++ b/TUCUMAN 1061/Agosto/tucuman Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97816A6A-0B30-40A2-A9EA-4BFF79CAA767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16621BA-D928-48CC-BDDA-A218690A92A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -551,19 +551,19 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t xml:space="preserve">PERIODO: JULIO </t>
-  </si>
-  <si>
-    <t>Poliza Sr. De Luca Carlos Hernan - La holando JULIO</t>
-  </si>
-  <si>
-    <t>Administraciòn JULIO 2025:</t>
-  </si>
-  <si>
     <t>subidos en juli 2025</t>
   </si>
   <si>
     <t>Protocolizacion de acta volante - Diferencia de certificados por rubricas de libros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERIODO: AGOSTO </t>
+  </si>
+  <si>
+    <t>Poliza Sr. De Luca Carlos Hernan - La holando AGOSTO</t>
+  </si>
+  <si>
+    <t>Administraciòn AGOSTO 2025:</t>
   </si>
 </sst>
 </file>
@@ -571,20 +571,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="14">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="0.000%"/>
-    <numFmt numFmtId="175" formatCode="0.00000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="0.00000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="37" x14ac:knownFonts="1">
     <font>
@@ -1352,16 +1352,16 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1377,86 +1377,86 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1465,7 +1465,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,22 +1478,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1503,25 +1503,25 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="170" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1533,34 +1533,34 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="36" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="36" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="37" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8" quotePrefix="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="13" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="28" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1"/>
@@ -1590,10 +1590,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1605,11 +1605,11 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1633,9 +1633,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1647,6 +1647,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="29" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1758,8 +1769,11 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1788,20 +1802,8 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2201,14 +2203,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2218,7 +2220,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -2228,18 +2230,18 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="189">
+      <c r="E3" s="194">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="189"/>
+      <c r="F3" s="194"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -2249,18 +2251,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="D5" s="42" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -2268,13 +2270,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2284,11 +2286,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -2297,7 +2299,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2307,19 +2309,19 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="199" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="199"/>
-      <c r="C12" s="199"/>
-      <c r="D12" s="199"/>
-      <c r="E12" s="199"/>
-      <c r="F12" s="199"/>
-      <c r="G12" s="199"/>
-      <c r="H12" s="199"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="204"/>
+      <c r="C12" s="204"/>
+      <c r="D12" s="204"/>
+      <c r="E12" s="204"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="204"/>
+      <c r="H12" s="204"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -2329,7 +2331,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>60</v>
       </c>
@@ -2341,13 +2343,13 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="238">
+      <c r="H14" s="190">
         <v>373590.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="98" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2355,11 +2357,11 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="238">
+      <c r="H15" s="241">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>5</v>
       </c>
@@ -2374,7 +2376,7 @@
         <v>377620.78</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
@@ -2384,19 +2386,19 @@
       <c r="G17" s="24"/>
       <c r="H17" s="43"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="200" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="201"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="201"/>
-      <c r="G18" s="201"/>
-      <c r="H18" s="202"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="206"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="206"/>
+      <c r="E18" s="206"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="206"/>
+      <c r="H18" s="207"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>59</v>
       </c>
@@ -2406,11 +2408,11 @@
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="26">
-        <v>177932.77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H19" s="240">
+        <v>371766.51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>58</v>
       </c>
@@ -2420,11 +2422,11 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="26">
-        <v>355749.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H20" s="240">
+        <v>513573.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
@@ -2436,23 +2438,23 @@
       <c r="G21" s="22"/>
       <c r="H21" s="27">
         <f>SUM(H19:H20)</f>
-        <v>533682.13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="203" t="s">
+        <v>885340.42999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="208" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="203"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="203"/>
+      <c r="B22" s="208"/>
+      <c r="C22" s="208"/>
+      <c r="D22" s="208"/>
+      <c r="E22" s="208"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="98" t="s">
         <v>142</v>
       </c>
@@ -2462,13 +2464,13 @@
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="26">
-        <v>42645</v>
+      <c r="H23" s="240">
+        <v>46638</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="98" t="s">
         <v>160</v>
       </c>
@@ -2484,7 +2486,7 @@
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="98" t="s">
         <v>144</v>
       </c>
@@ -2494,11 +2496,11 @@
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
-      <c r="H25" s="26">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H25" s="240">
+        <v>77800</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>8</v>
       </c>
@@ -2510,22 +2512,22 @@
       <c r="G26" s="22"/>
       <c r="H26" s="27">
         <f>SUM(H23:H25)</f>
-        <v>156985</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="200" t="s">
+        <v>173778</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="205" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="201"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="201"/>
-      <c r="E27" s="201"/>
-      <c r="F27" s="201"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="202"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="206"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="206"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="207"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>9</v>
       </c>
@@ -2540,9 +2542,9 @@
       <c r="H28" s="28"/>
       <c r="I28" s="44"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -2550,15 +2552,15 @@
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
-      <c r="H29" s="239">
+      <c r="H29" s="191">
         <v>66600</v>
       </c>
       <c r="I29" s="44"/>
       <c r="N29" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -2568,19 +2570,19 @@
       <c r="G30" s="19"/>
       <c r="H30" s="29"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="200" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="205" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="201"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="201"/>
-      <c r="F31" s="201"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="202"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="206"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="207"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="50"/>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -2591,7 +2593,7 @@
       <c r="H32" s="52"/>
       <c r="J32" s="15"/>
     </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>15</v>
       </c>
@@ -2603,10 +2605,10 @@
       <c r="G33" s="31"/>
       <c r="H33" s="32">
         <f>H16+H21+H26+H29+H32</f>
-        <v>1134887.9100000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+        <v>1503339.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="s">
         <v>151</v>
       </c>
@@ -2618,110 +2620,110 @@
       <c r="G34" s="47"/>
       <c r="H34" s="48"/>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="190" t="s">
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="195" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="191"/>
-      <c r="C35" s="191"/>
-      <c r="D35" s="191"/>
-      <c r="E35" s="191"/>
-      <c r="F35" s="191"/>
-      <c r="G35" s="191"/>
-      <c r="H35" s="192"/>
+      <c r="B35" s="196"/>
+      <c r="C35" s="196"/>
+      <c r="D35" s="196"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="197"/>
       <c r="I35" s="167"/>
       <c r="K35" s="167"/>
     </row>
-    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="193"/>
-      <c r="B36" s="194"/>
-      <c r="C36" s="194"/>
-      <c r="D36" s="194"/>
-      <c r="E36" s="194"/>
-      <c r="F36" s="194"/>
-      <c r="G36" s="194"/>
-      <c r="H36" s="195"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="204" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="205"/>
-      <c r="C37" s="205"/>
-      <c r="D37" s="205"/>
-      <c r="E37" s="205"/>
-      <c r="F37" s="205"/>
-      <c r="G37" s="206"/>
-      <c r="H37" s="236">
+    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="198"/>
+      <c r="B36" s="199"/>
+      <c r="C36" s="199"/>
+      <c r="D36" s="199"/>
+      <c r="E36" s="199"/>
+      <c r="F36" s="199"/>
+      <c r="G36" s="199"/>
+      <c r="H36" s="200"/>
+    </row>
+    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="209" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="210"/>
+      <c r="C37" s="210"/>
+      <c r="D37" s="210"/>
+      <c r="E37" s="210"/>
+      <c r="F37" s="210"/>
+      <c r="G37" s="211"/>
+      <c r="H37" s="189">
         <v>470300</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="204"/>
-      <c r="B38" s="205"/>
-      <c r="C38" s="205"/>
-      <c r="D38" s="205"/>
-      <c r="E38" s="205"/>
-      <c r="F38" s="205"/>
-      <c r="G38" s="206"/>
+    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="209"/>
+      <c r="B38" s="210"/>
+      <c r="C38" s="210"/>
+      <c r="D38" s="210"/>
+      <c r="E38" s="210"/>
+      <c r="F38" s="210"/>
+      <c r="G38" s="211"/>
       <c r="H38" s="33"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="207"/>
-      <c r="B39" s="208"/>
-      <c r="C39" s="208"/>
-      <c r="D39" s="208"/>
-      <c r="E39" s="208"/>
-      <c r="F39" s="208"/>
-      <c r="G39" s="209"/>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="212"/>
+      <c r="B39" s="213"/>
+      <c r="C39" s="213"/>
+      <c r="D39" s="213"/>
+      <c r="E39" s="213"/>
+      <c r="F39" s="213"/>
+      <c r="G39" s="214"/>
       <c r="H39" s="33"/>
     </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="210" t="s">
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="211"/>
-      <c r="C40" s="211"/>
-      <c r="D40" s="211"/>
-      <c r="E40" s="211"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="212"/>
+      <c r="B40" s="216"/>
+      <c r="C40" s="216"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="217"/>
       <c r="H40" s="34">
         <f>SUM(H37:H39)</f>
         <v>470300</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="234"/>
-      <c r="B41" s="234"/>
-      <c r="C41" s="234"/>
-      <c r="D41" s="234"/>
-      <c r="E41" s="234"/>
-      <c r="F41" s="234"/>
-      <c r="G41" s="234"/>
-      <c r="H41" s="235"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="187"/>
+      <c r="B41" s="187"/>
+      <c r="C41" s="187"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="187"/>
+      <c r="H41" s="188"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H42" s="19"/>
       <c r="J42" s="15"/>
     </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="187" t="s">
+    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="192" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="187"/>
-      <c r="C43" s="187"/>
-      <c r="D43" s="187"/>
-      <c r="E43" s="187"/>
-      <c r="F43" s="187"/>
-      <c r="G43" s="187"/>
+      <c r="B43" s="192"/>
+      <c r="C43" s="192"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
+      <c r="F43" s="192"/>
+      <c r="G43" s="192"/>
       <c r="H43" s="32">
         <f>+H33+H34</f>
-        <v>1134887.9100000001</v>
+        <v>1503339.21</v>
       </c>
       <c r="J43" s="167"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -2731,7 +2733,7 @@
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
     </row>
-    <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
         <v>155</v>
       </c>
@@ -2746,7 +2748,7 @@
         <v>470300</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -2756,33 +2758,33 @@
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
     </row>
-    <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="196" t="s">
+    <row r="47" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="197"/>
-      <c r="C47" s="197"/>
-      <c r="D47" s="197"/>
-      <c r="E47" s="197"/>
-      <c r="F47" s="197"/>
-      <c r="G47" s="197"/>
-      <c r="H47" s="198"/>
-    </row>
-    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="188" t="s">
+      <c r="B47" s="202"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="202"/>
+      <c r="F47" s="202"/>
+      <c r="G47" s="202"/>
+      <c r="H47" s="203"/>
+    </row>
+    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="193" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="188"/>
-      <c r="C48" s="188"/>
-      <c r="D48" s="188"/>
-      <c r="E48" s="188"/>
-      <c r="F48" s="188"/>
-      <c r="G48" s="188"/>
+      <c r="B48" s="193"/>
+      <c r="C48" s="193"/>
+      <c r="D48" s="193"/>
+      <c r="E48" s="193"/>
+      <c r="F48" s="193"/>
+      <c r="G48" s="193"/>
       <c r="H48" s="41">
         <v>1958258.8766773101</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="36" t="s">
         <v>149</v>
       </c>
@@ -2797,7 +2799,7 @@
         <v>1480247.3410500004</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="36" t="s">
         <v>150</v>
       </c>
@@ -2809,11 +2811,11 @@
       <c r="G50" s="37"/>
       <c r="H50" s="38">
         <f>-(H33+H40)</f>
-        <v>-1605187.9100000001</v>
+        <v>-1973639.21</v>
       </c>
       <c r="J50" s="15"/>
     </row>
-    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="39" t="s">
         <v>14</v>
       </c>
@@ -2825,7 +2827,7 @@
       <c r="G51" s="40"/>
       <c r="H51" s="49">
         <f>SUM(H48:H50)</f>
-        <v>1833318.3077273103</v>
+        <v>1464867.0077273105</v>
       </c>
     </row>
   </sheetData>
@@ -2860,53 +2862,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="53" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="55" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="54" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="54" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="54" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="54" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="54" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="54" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="53" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="54" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="54" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="54" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" style="54" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" style="54" customWidth="1"/>
+    <col min="12" max="12" width="0.109375" style="54" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="216" t="str">
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="221" t="str">
         <f>Gastos!E7</f>
-        <v xml:space="preserve">PERIODO: JULIO </v>
-      </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="218"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">PERIODO: AGOSTO </v>
+      </c>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="223"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="92"/>
       <c r="C2" s="183">
         <v>1134887.9100000001</v>
@@ -2919,7 +2921,7 @@
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="88"/>
       <c r="D3" s="183">
         <v>355749.36</v>
@@ -2931,7 +2933,7 @@
       <c r="L3" s="90"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="88"/>
       <c r="C4" s="13" t="s">
         <v>158</v>
@@ -2942,21 +2944,21 @@
       <c r="I4" s="56"/>
       <c r="J4" s="56"/>
       <c r="L4" s="90"/>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="215"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="220"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="88"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="224">
+      <c r="C5" s="229">
         <f>D3</f>
         <v>355749.36</v>
       </c>
-      <c r="D5" s="224"/>
+      <c r="D5" s="229"/>
       <c r="E5" s="13"/>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
@@ -2966,7 +2968,7 @@
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="88"/>
       <c r="C6" s="13" t="s">
         <v>157</v>
@@ -2981,14 +2983,14 @@
       <c r="L6" s="56"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="88"/>
       <c r="B7" s="87"/>
-      <c r="C7" s="224">
+      <c r="C7" s="229">
         <f>C2-D3</f>
         <v>779138.55000000016</v>
       </c>
-      <c r="D7" s="224"/>
+      <c r="D7" s="229"/>
       <c r="E7" s="89"/>
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
@@ -2998,7 +3000,7 @@
       <c r="L7" s="56"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="88"/>
       <c r="B8" s="87"/>
       <c r="C8" s="87" t="s">
@@ -3014,13 +3016,13 @@
       <c r="L8" s="56"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="86"/>
       <c r="B9" s="85"/>
-      <c r="C9" s="237">
+      <c r="C9" s="230">
         <v>470300</v>
       </c>
-      <c r="D9" s="237"/>
+      <c r="D9" s="230"/>
       <c r="E9" s="84"/>
       <c r="F9" s="83"/>
       <c r="G9" s="82"/>
@@ -3036,7 +3038,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="80" t="s">
         <v>32</v>
       </c>
@@ -3092,7 +3094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="174" t="s">
         <v>81</v>
       </c>
@@ -3154,7 +3156,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="168" t="s">
         <v>82</v>
       </c>
@@ -3216,7 +3218,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="160" t="s">
         <v>83</v>
       </c>
@@ -3280,7 +3282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="110" t="s">
         <v>84</v>
       </c>
@@ -3340,7 +3342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="110" t="s">
         <v>85</v>
       </c>
@@ -3399,7 +3401,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="160" t="s">
         <v>86</v>
       </c>
@@ -3461,7 +3463,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="110" t="s">
         <v>87</v>
       </c>
@@ -3525,7 +3527,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="160" t="s">
         <v>88</v>
       </c>
@@ -3586,7 +3588,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="160" t="s">
         <v>89</v>
       </c>
@@ -3650,7 +3652,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="110" t="s">
         <v>90</v>
       </c>
@@ -3707,7 +3709,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="160" t="s">
         <v>91</v>
       </c>
@@ -3766,7 +3768,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="160" t="s">
         <v>92</v>
       </c>
@@ -3823,7 +3825,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="110"/>
       <c r="B23" s="71"/>
       <c r="C23" s="94" t="s">
@@ -3878,7 +3880,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="160"/>
       <c r="B24" s="161"/>
       <c r="C24" s="95" t="s">
@@ -3936,7 +3938,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="110"/>
       <c r="B25" s="71"/>
       <c r="C25" s="94" t="s">
@@ -3992,7 +3994,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="160"/>
       <c r="B26" s="157"/>
       <c r="C26" s="95" t="s">
@@ -4052,7 +4054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="110"/>
       <c r="B27" s="71"/>
       <c r="C27" s="94" t="s">
@@ -4110,7 +4112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="184"/>
       <c r="B28" s="185"/>
       <c r="C28" s="95" t="s">
@@ -4170,7 +4172,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="160"/>
       <c r="B29" s="173"/>
       <c r="C29" s="95" t="s">
@@ -4230,7 +4232,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="73"/>
       <c r="B30" s="71"/>
       <c r="C30" s="70"/>
@@ -4258,10 +4260,10 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="222"/>
-      <c r="B31" s="223"/>
-      <c r="C31" s="223"/>
+    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="227"/>
+      <c r="B31" s="228"/>
+      <c r="C31" s="228"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
       <c r="F31" s="97"/>
@@ -4305,31 +4307,31 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="219" t="s">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="220"/>
-      <c r="D32" s="220"/>
-      <c r="E32" s="220"/>
-      <c r="F32" s="220"/>
-      <c r="G32" s="220"/>
-      <c r="H32" s="220"/>
-      <c r="I32" s="220"/>
-      <c r="J32" s="220"/>
-      <c r="K32" s="220"/>
-      <c r="L32" s="220"/>
-      <c r="M32" s="220"/>
-      <c r="N32" s="220"/>
-      <c r="O32" s="220"/>
-      <c r="P32" s="220"/>
-      <c r="Q32" s="220"/>
-      <c r="R32" s="221"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="225"/>
+      <c r="N32" s="225"/>
+      <c r="O32" s="225"/>
+      <c r="P32" s="225"/>
+      <c r="Q32" s="225"/>
+      <c r="R32" s="226"/>
       <c r="U32" s="94" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
       <c r="F33" s="57"/>
       <c r="G33" s="56"/>
       <c r="H33" s="56"/>
@@ -4343,80 +4345,80 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="213"/>
-      <c r="D34" s="213"/>
-      <c r="E34" s="213"/>
-      <c r="F34" s="213"/>
-      <c r="G34" s="213"/>
-      <c r="H34" s="213"/>
-      <c r="I34" s="213"/>
-      <c r="J34" s="213"/>
-      <c r="K34" s="213"/>
-      <c r="L34" s="213"/>
-      <c r="M34" s="213"/>
-      <c r="N34" s="213"/>
-      <c r="O34" s="213"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="213"/>
-      <c r="D35" s="213"/>
-      <c r="E35" s="213"/>
-      <c r="F35" s="213"/>
-      <c r="G35" s="213"/>
-      <c r="H35" s="213"/>
-      <c r="I35" s="213"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="213"/>
-      <c r="M35" s="213"/>
-      <c r="N35" s="213"/>
-      <c r="O35" s="213"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="213"/>
-      <c r="D36" s="213"/>
-      <c r="E36" s="213"/>
-      <c r="F36" s="213"/>
-      <c r="G36" s="213"/>
-      <c r="H36" s="213"/>
-      <c r="I36" s="213"/>
-      <c r="J36" s="213"/>
-      <c r="K36" s="213"/>
-      <c r="L36" s="213"/>
-      <c r="M36" s="213"/>
-      <c r="N36" s="213"/>
-      <c r="O36" s="213"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="213"/>
-      <c r="D37" s="213"/>
-      <c r="E37" s="213"/>
-      <c r="F37" s="213"/>
-      <c r="G37" s="213"/>
-      <c r="H37" s="213"/>
-      <c r="I37" s="213"/>
-      <c r="J37" s="213"/>
-      <c r="K37" s="213"/>
-      <c r="L37" s="213"/>
-      <c r="M37" s="213"/>
-      <c r="N37" s="213"/>
-      <c r="O37" s="213"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="213"/>
-      <c r="D38" s="213"/>
-      <c r="E38" s="213"/>
-      <c r="F38" s="213"/>
-      <c r="G38" s="213"/>
-      <c r="H38" s="213"/>
-      <c r="I38" s="213"/>
-      <c r="J38" s="213"/>
-      <c r="K38" s="213"/>
-      <c r="L38" s="213"/>
-      <c r="M38" s="213"/>
-      <c r="N38" s="213"/>
-      <c r="O38" s="213"/>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C34" s="218"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="218"/>
+      <c r="I34" s="218"/>
+      <c r="J34" s="218"/>
+      <c r="K34" s="218"/>
+      <c r="L34" s="218"/>
+      <c r="M34" s="218"/>
+      <c r="N34" s="218"/>
+      <c r="O34" s="218"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C35" s="218"/>
+      <c r="D35" s="218"/>
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="218"/>
+      <c r="H35" s="218"/>
+      <c r="I35" s="218"/>
+      <c r="J35" s="218"/>
+      <c r="K35" s="218"/>
+      <c r="L35" s="218"/>
+      <c r="M35" s="218"/>
+      <c r="N35" s="218"/>
+      <c r="O35" s="218"/>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
+      <c r="I36" s="218"/>
+      <c r="J36" s="218"/>
+      <c r="K36" s="218"/>
+      <c r="L36" s="218"/>
+      <c r="M36" s="218"/>
+      <c r="N36" s="218"/>
+      <c r="O36" s="218"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C37" s="218"/>
+      <c r="D37" s="218"/>
+      <c r="E37" s="218"/>
+      <c r="F37" s="218"/>
+      <c r="G37" s="218"/>
+      <c r="H37" s="218"/>
+      <c r="I37" s="218"/>
+      <c r="J37" s="218"/>
+      <c r="K37" s="218"/>
+      <c r="L37" s="218"/>
+      <c r="M37" s="218"/>
+      <c r="N37" s="218"/>
+      <c r="O37" s="218"/>
+    </row>
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="218"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
+      <c r="H38" s="218"/>
+      <c r="I38" s="218"/>
+      <c r="J38" s="218"/>
+      <c r="K38" s="218"/>
+      <c r="L38" s="218"/>
+      <c r="M38" s="218"/>
+      <c r="N38" s="218"/>
+      <c r="O38" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4438,31 +4440,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="114" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="114" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="114" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="114" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.44140625" style="114" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="114" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="114"/>
-    <col min="13" max="13" width="14.7109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="114" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="114"/>
+    <col min="9" max="12" width="11.44140625" style="114"/>
+    <col min="13" max="13" width="14.6640625" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="114" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="225" t="s">
+    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="231" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="227"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B1" s="232"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="233"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="155"/>
       <c r="B2" s="140"/>
       <c r="C2" s="140"/>
@@ -4471,7 +4473,7 @@
       </c>
       <c r="E2" s="151"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="153">
         <f>13+28+19</f>
         <v>60</v>
@@ -4493,38 +4495,38 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="150"/>
       <c r="B4" s="149"/>
       <c r="C4" s="149"/>
       <c r="D4" s="149"/>
       <c r="E4" s="148"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="147"/>
       <c r="B5" s="147"/>
       <c r="C5" s="147"/>
       <c r="D5" s="147"/>
       <c r="E5" s="147"/>
     </row>
-    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="147"/>
       <c r="B6" s="147"/>
       <c r="C6" s="147"/>
       <c r="D6" s="147"/>
       <c r="E6" s="147"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="228" t="s">
+    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="234" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="229"/>
-      <c r="C7" s="229"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="229"/>
-      <c r="H7" s="230"/>
+      <c r="B7" s="235"/>
+      <c r="C7" s="235"/>
+      <c r="D7" s="235"/>
+      <c r="E7" s="235"/>
+      <c r="F7" s="235"/>
+      <c r="G7" s="235"/>
+      <c r="H7" s="236"/>
       <c r="L7" s="114" t="s">
         <v>72</v>
       </c>
@@ -4532,7 +4534,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="107">
         <v>400523.88</v>
       </c>
@@ -4568,7 +4570,7 @@
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="143" t="s">
         <v>34</v>
       </c>
@@ -4617,7 +4619,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="141" t="s">
         <v>35</v>
       </c>
@@ -4666,7 +4668,7 @@
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="141" t="s">
         <v>36</v>
       </c>
@@ -4714,7 +4716,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="141" t="s">
         <v>37</v>
       </c>
@@ -4761,7 +4763,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="141" t="s">
         <v>38</v>
       </c>
@@ -4804,7 +4806,7 @@
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="141" t="s">
         <v>39</v>
       </c>
@@ -4839,7 +4841,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="141" t="s">
         <v>40</v>
       </c>
@@ -4878,7 +4880,7 @@
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="141" t="s">
         <v>41</v>
       </c>
@@ -4913,7 +4915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="141" t="s">
         <v>42</v>
       </c>
@@ -4948,7 +4950,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="141" t="s">
         <v>43</v>
       </c>
@@ -4983,7 +4985,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="141" t="s">
         <v>44</v>
       </c>
@@ -5018,7 +5020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="141" t="s">
         <v>45</v>
       </c>
@@ -5050,7 +5052,7 @@
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="139" t="s">
         <v>139</v>
       </c>
@@ -5072,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="100">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
@@ -5082,7 +5084,7 @@
       </c>
       <c r="L22" s="134"/>
     </row>
-    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="99">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
@@ -5091,35 +5093,35 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="132"/>
       <c r="J25" s="114">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J26" s="114">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J27" s="114">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="231" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="237" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="232"/>
-      <c r="D28" s="232"/>
-      <c r="E28" s="232"/>
-      <c r="F28" s="233"/>
+      <c r="C28" s="238"/>
+      <c r="D28" s="238"/>
+      <c r="E28" s="238"/>
+      <c r="F28" s="239"/>
       <c r="J28" s="114">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="131" t="s">
         <v>137</v>
       </c>
@@ -5139,7 +5141,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="125" t="s">
         <v>132</v>
       </c>
@@ -5162,7 +5164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="125" t="s">
         <v>131</v>
       </c>
@@ -5181,7 +5183,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="125" t="s">
         <v>130</v>
       </c>
@@ -5200,7 +5202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="125" t="s">
         <v>129</v>
       </c>
@@ -5223,7 +5225,7 @@
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="125" t="s">
         <v>128</v>
       </c>
@@ -5242,7 +5244,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="125" t="s">
         <v>127</v>
       </c>
@@ -5261,7 +5263,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="125" t="s">
         <v>126</v>
       </c>
@@ -5280,7 +5282,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="125" t="s">
         <v>125</v>
       </c>
@@ -5296,7 +5298,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="125" t="s">
         <v>124</v>
       </c>
@@ -5318,7 +5320,7 @@
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="125" t="s">
         <v>122</v>
       </c>
@@ -5332,7 +5334,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" s="125" t="s">
         <v>121</v>
       </c>
@@ -5346,7 +5348,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B41" s="125" t="s">
         <v>120</v>
       </c>
@@ -5360,7 +5362,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="125" t="s">
         <v>119</v>
       </c>
@@ -5374,7 +5376,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="125" t="s">
         <v>118</v>
       </c>
@@ -5388,7 +5390,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="122" t="s">
         <v>117</v>
       </c>
@@ -5402,7 +5404,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="122" t="s">
         <v>116</v>
       </c>
@@ -5416,7 +5418,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="122" t="s">
         <v>115</v>
       </c>
@@ -5430,7 +5432,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="118" t="s">
         <v>114</v>
       </c>

--- a/TUCUMAN 1061/Agosto/tucuman Agosto.xlsx
+++ b/TUCUMAN 1061/Agosto/tucuman Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16621BA-D928-48CC-BDDA-A218690A92A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BFAA8A-5D67-47DA-A515-9DBAD3B4A64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="166">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -548,15 +548,9 @@
     <t>Perez Sebastian</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>subidos en juli 2025</t>
   </si>
   <si>
-    <t>Protocolizacion de acta volante - Diferencia de certificados por rubricas de libros</t>
-  </si>
-  <si>
     <t xml:space="preserve">PERIODO: AGOSTO </t>
   </si>
   <si>
@@ -564,6 +558,12 @@
   </si>
   <si>
     <t>Administraciòn AGOSTO 2025:</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>Digitalizacion de copias - Escrbania Narosky</t>
   </si>
 </sst>
 </file>
@@ -571,20 +571,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="14">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.000%"/>
-    <numFmt numFmtId="172" formatCode="0.00000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="0.000%"/>
+    <numFmt numFmtId="175" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="37" x14ac:knownFonts="1">
     <font>
@@ -1352,16 +1352,16 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1377,86 +1377,86 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1465,7 +1465,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,22 +1478,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1503,25 +1503,25 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="25" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="167" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="7" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1533,34 +1533,34 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="23" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="24" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="36" xfId="7" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="36" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="18" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="37" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="3" xfId="8" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="32" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="32" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="8" quotePrefix="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="13" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="20" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="26" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="28" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="3" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="25" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="29" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="28" xfId="8" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="19" xfId="8" applyFont="1" applyBorder="1"/>
@@ -1590,10 +1590,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1605,11 +1605,11 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="32" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1633,9 +1633,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="21" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1650,14 +1650,11 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1769,10 +1766,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1802,8 +1799,9 @@
     <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2202,15 +2200,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2220,7 +2218,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -2230,18 +2228,18 @@
       </c>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="194">
+      <c r="E3" s="193">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="194"/>
+      <c r="F3" s="193"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
@@ -2251,18 +2249,18 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="D5" s="42" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>3</v>
       </c>
@@ -2270,13 +2268,13 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2286,11 +2284,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -2299,7 +2297,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2309,19 +2307,19 @@
       <c r="G11" s="2"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="204" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="204"/>
-      <c r="C12" s="204"/>
-      <c r="D12" s="204"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="204"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="203"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="203"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -2331,7 +2329,7 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>60</v>
       </c>
@@ -2343,13 +2341,14 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="190">
-        <v>373590.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="189">
+        <f>373590.5+373591*5%</f>
+        <v>392270.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2357,11 +2356,11 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="241">
+      <c r="H15" s="189">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>5</v>
       </c>
@@ -2373,10 +2372,10 @@
       <c r="G16" s="22"/>
       <c r="H16" s="181">
         <f>SUM(H13:H15)</f>
-        <v>377620.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>396300.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
@@ -2386,19 +2385,19 @@
       <c r="G17" s="24"/>
       <c r="H17" s="43"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="205" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="206"/>
-      <c r="C18" s="206"/>
-      <c r="D18" s="206"/>
-      <c r="E18" s="206"/>
-      <c r="F18" s="206"/>
-      <c r="G18" s="206"/>
-      <c r="H18" s="207"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="205"/>
+      <c r="C18" s="205"/>
+      <c r="D18" s="205"/>
+      <c r="E18" s="205"/>
+      <c r="F18" s="205"/>
+      <c r="G18" s="205"/>
+      <c r="H18" s="206"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>59</v>
       </c>
@@ -2408,11 +2407,11 @@
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="240">
+      <c r="H19" s="26">
         <v>371766.51</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>58</v>
       </c>
@@ -2422,11 +2421,11 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="240">
+      <c r="H20" s="26">
         <v>513573.92</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
@@ -2441,20 +2440,20 @@
         <v>885340.42999999993</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="208" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="208"/>
-      <c r="C22" s="208"/>
-      <c r="D22" s="208"/>
-      <c r="E22" s="208"/>
-      <c r="F22" s="208"/>
-      <c r="G22" s="208"/>
-      <c r="H22" s="208"/>
+      <c r="B22" s="207"/>
+      <c r="C22" s="207"/>
+      <c r="D22" s="207"/>
+      <c r="E22" s="207"/>
+      <c r="F22" s="207"/>
+      <c r="G22" s="207"/>
+      <c r="H22" s="207"/>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
         <v>142</v>
       </c>
@@ -2464,329 +2463,328 @@
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="240">
+      <c r="H23" s="26">
         <v>46638</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="98" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B24" s="19"/>
-      <c r="C24" s="25"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="26">
-        <v>49340</v>
-      </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="98" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="240">
         <v>77800</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="27">
-        <f>SUM(H23:H25)</f>
-        <v>173778</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="205" t="s">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="27">
+        <f>SUM(H23:H24)</f>
+        <v>124438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="204" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="207"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="B26" s="205"/>
+      <c r="C26" s="205"/>
+      <c r="D26" s="205"/>
+      <c r="E26" s="205"/>
+      <c r="F26" s="205"/>
+      <c r="G26" s="205"/>
+      <c r="H26" s="206"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19" t="s">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="28"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="44"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="190">
+        <v>66600</v>
+      </c>
       <c r="I28" s="44"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
+      <c r="N28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="29"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="204" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="205"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="205"/>
+      <c r="E30" s="205"/>
+      <c r="F30" s="205"/>
+      <c r="G30" s="205"/>
+      <c r="H30" s="206"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="50"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="32">
+        <f>H16+H21+H25+H28+H31</f>
+        <v>1472678.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="194" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="195"/>
+      <c r="C34" s="195"/>
+      <c r="D34" s="195"/>
+      <c r="E34" s="195"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="195"/>
+      <c r="H34" s="196"/>
+      <c r="I34" s="167"/>
+      <c r="K34" s="167"/>
+    </row>
+    <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="197"/>
+      <c r="B35" s="198"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="199"/>
+    </row>
+    <row r="36" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="208" t="s">
         <v>165</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="191">
-        <v>66600</v>
-      </c>
-      <c r="I29" s="44"/>
-      <c r="N29" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="29"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="205" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="206"/>
-      <c r="D31" s="206"/>
-      <c r="E31" s="206"/>
-      <c r="F31" s="206"/>
-      <c r="G31" s="206"/>
-      <c r="H31" s="207"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="52"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32">
-        <f>H16+H21+H26+H29+H32</f>
-        <v>1503339.21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="48"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="195" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="196"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="197"/>
-      <c r="I35" s="167"/>
-      <c r="K35" s="167"/>
-    </row>
-    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="198"/>
-      <c r="B36" s="199"/>
-      <c r="C36" s="199"/>
-      <c r="D36" s="199"/>
-      <c r="E36" s="199"/>
-      <c r="F36" s="199"/>
-      <c r="G36" s="199"/>
-      <c r="H36" s="200"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="209" t="s">
-        <v>162</v>
-      </c>
-      <c r="B37" s="210"/>
-      <c r="C37" s="210"/>
-      <c r="D37" s="210"/>
-      <c r="E37" s="210"/>
-      <c r="F37" s="210"/>
-      <c r="G37" s="211"/>
-      <c r="H37" s="189">
-        <v>470300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="209"/>
-      <c r="B38" s="210"/>
-      <c r="C38" s="210"/>
-      <c r="D38" s="210"/>
-      <c r="E38" s="210"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="211"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="209"/>
+      <c r="D36" s="209"/>
+      <c r="E36" s="209"/>
+      <c r="F36" s="209"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="239">
+        <v>110800</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="208"/>
+      <c r="B37" s="209"/>
+      <c r="C37" s="209"/>
+      <c r="D37" s="209"/>
+      <c r="E37" s="209"/>
+      <c r="F37" s="209"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="33"/>
+    </row>
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="211"/>
+      <c r="B38" s="212"/>
+      <c r="C38" s="212"/>
+      <c r="D38" s="212"/>
+      <c r="E38" s="212"/>
+      <c r="F38" s="212"/>
+      <c r="G38" s="213"/>
       <c r="H38" s="33"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="212"/>
-      <c r="B39" s="213"/>
-      <c r="C39" s="213"/>
-      <c r="D39" s="213"/>
-      <c r="E39" s="213"/>
-      <c r="F39" s="213"/>
-      <c r="G39" s="214"/>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="215" t="s">
+    <row r="39" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="216"/>
-      <c r="C40" s="216"/>
-      <c r="D40" s="216"/>
-      <c r="E40" s="216"/>
-      <c r="F40" s="216"/>
-      <c r="G40" s="217"/>
-      <c r="H40" s="34">
-        <f>SUM(H37:H39)</f>
-        <v>470300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="187"/>
-      <c r="B41" s="187"/>
-      <c r="C41" s="187"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="187"/>
-      <c r="F41" s="187"/>
-      <c r="G41" s="187"/>
-      <c r="H41" s="188"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H42" s="19"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="192" t="s">
+      <c r="B39" s="215"/>
+      <c r="C39" s="215"/>
+      <c r="D39" s="215"/>
+      <c r="E39" s="215"/>
+      <c r="F39" s="215"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="34">
+        <f>SUM(H36:H38)</f>
+        <v>110800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="187"/>
+      <c r="B40" s="187"/>
+      <c r="C40" s="187"/>
+      <c r="D40" s="187"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="187"/>
+      <c r="H40" s="188"/>
+    </row>
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" s="19"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="191" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="192"/>
-      <c r="C43" s="192"/>
-      <c r="D43" s="192"/>
-      <c r="E43" s="192"/>
-      <c r="F43" s="192"/>
-      <c r="G43" s="192"/>
-      <c r="H43" s="32">
-        <f>+H33+H34</f>
-        <v>1503339.21</v>
-      </c>
-      <c r="J43" s="167"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
+      <c r="B42" s="191"/>
+      <c r="C42" s="191"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="191"/>
+      <c r="H42" s="32">
+        <f>+H32+H33</f>
+        <v>1472678.76</v>
+      </c>
+      <c r="J42" s="167"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="35">
-        <f>H40</f>
-        <v>470300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="201" t="s">
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="35">
+        <f>H39</f>
+        <v>110800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="202"/>
-      <c r="C47" s="202"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="202"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="202"/>
-      <c r="H47" s="203"/>
-    </row>
-    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="193" t="s">
+      <c r="B46" s="201"/>
+      <c r="C46" s="201"/>
+      <c r="D46" s="201"/>
+      <c r="E46" s="201"/>
+      <c r="F46" s="201"/>
+      <c r="G46" s="201"/>
+      <c r="H46" s="202"/>
+    </row>
+    <row r="47" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="192" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="193"/>
-      <c r="C48" s="193"/>
-      <c r="D48" s="193"/>
-      <c r="E48" s="193"/>
-      <c r="F48" s="193"/>
-      <c r="G48" s="193"/>
-      <c r="H48" s="41">
-        <v>1958258.8766773101</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="192"/>
+      <c r="C47" s="192"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="192"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="41">
+        <v>1833318.3077273103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="45">
+        <f>Planilla!I31</f>
+        <v>1987845.22483</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B49" s="37"/>
       <c r="C49" s="37"/>
@@ -2794,58 +2792,43 @@
       <c r="E49" s="37"/>
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
-      <c r="H49" s="45">
-        <f>Planilla!I31</f>
-        <v>1480247.3410500004</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38">
-        <f>-(H33+H40)</f>
-        <v>-1973639.21</v>
-      </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A51" s="39" t="s">
+      <c r="H49" s="38">
+        <f>-(H32+H39)</f>
+        <v>-1583478.76</v>
+      </c>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="49">
-        <f>SUM(H48:H50)</f>
-        <v>1464867.0077273105</v>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="49">
+        <f>SUM(H47:H49)</f>
+        <v>2237684.7725573108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A34:H35"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2862,56 +2845,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" style="53" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="55" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="54" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" style="54" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" style="54" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" style="54" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" style="54" customWidth="1"/>
-    <col min="12" max="12" width="0.109375" style="54" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="53" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.28515625" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="54" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="54" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="54" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" style="54" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="54" customWidth="1"/>
+    <col min="12" max="12" width="0.140625" style="54" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="str">
+    <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="220" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: AGOSTO </v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="223"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="221"/>
+      <c r="P1" s="221"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="222"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="92"/>
       <c r="C2" s="183">
-        <v>1134887.9100000001</v>
+        <v>1472678.76</v>
       </c>
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
@@ -2921,10 +2904,10 @@
       <c r="L2" s="13"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="88"/>
       <c r="D3" s="183">
-        <v>355749.36</v>
+        <v>513573.92</v>
       </c>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
@@ -2933,7 +2916,7 @@
       <c r="L3" s="90"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="88"/>
       <c r="C4" s="13" t="s">
         <v>158</v>
@@ -2944,21 +2927,21 @@
       <c r="I4" s="56"/>
       <c r="J4" s="56"/>
       <c r="L4" s="90"/>
-      <c r="M4" s="219"/>
-      <c r="N4" s="219"/>
-      <c r="O4" s="219"/>
-      <c r="P4" s="219"/>
-      <c r="Q4" s="219"/>
-      <c r="R4" s="220"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="219"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="91"/>
-      <c r="C5" s="229">
+      <c r="C5" s="228">
         <f>D3</f>
-        <v>355749.36</v>
-      </c>
-      <c r="D5" s="229"/>
+        <v>513573.92</v>
+      </c>
+      <c r="D5" s="228"/>
       <c r="E5" s="13"/>
       <c r="G5" s="56"/>
       <c r="H5" s="56"/>
@@ -2968,7 +2951,7 @@
       <c r="M5" s="17"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="88"/>
       <c r="C6" s="13" t="s">
         <v>157</v>
@@ -2983,14 +2966,14 @@
       <c r="L6" s="56"/>
       <c r="R6" s="6"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="88"/>
       <c r="B7" s="87"/>
-      <c r="C7" s="229">
+      <c r="C7" s="228">
         <f>C2-D3</f>
-        <v>779138.55000000016</v>
-      </c>
-      <c r="D7" s="229"/>
+        <v>959104.84000000008</v>
+      </c>
+      <c r="D7" s="228"/>
       <c r="E7" s="89"/>
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
@@ -3000,7 +2983,7 @@
       <c r="L7" s="56"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="88"/>
       <c r="B8" s="87"/>
       <c r="C8" s="87" t="s">
@@ -3016,13 +2999,13 @@
       <c r="L8" s="56"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="86"/>
       <c r="B9" s="85"/>
-      <c r="C9" s="230">
-        <v>470300</v>
-      </c>
-      <c r="D9" s="230"/>
+      <c r="C9" s="229">
+        <v>110000</v>
+      </c>
+      <c r="D9" s="229"/>
       <c r="E9" s="84"/>
       <c r="F9" s="83"/>
       <c r="G9" s="82"/>
@@ -3038,7 +3021,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="80" t="s">
         <v>32</v>
       </c>
@@ -3094,7 +3077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="174" t="s">
         <v>81</v>
       </c>
@@ -3110,14 +3093,14 @@
         <v>7.9</v>
       </c>
       <c r="G11" s="67">
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="H11" s="67">
         <v>0</v>
       </c>
       <c r="I11" s="67">
         <f>G11</f>
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="J11" s="67" t="e">
         <f>C8*F11/100</f>
@@ -3138,25 +3121,25 @@
       </c>
       <c r="O11" s="67">
         <f>C$7*F11/100</f>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P11" s="67">
         <f>C$9*F11/100</f>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q11" s="67">
         <f>C$5*F11/100</f>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R11" s="179">
         <f t="shared" ref="R11:R29" si="2">O11+N11+P11+Q11</f>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="U11" s="93" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="168" t="s">
         <v>82</v>
       </c>
@@ -3172,14 +3155,14 @@
         <v>7.9</v>
       </c>
       <c r="G12" s="159">
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="H12" s="159">
         <v>0</v>
       </c>
       <c r="I12" s="67">
         <f>G12</f>
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="J12" s="159" t="e">
         <f>C8*F12/100</f>
@@ -3200,25 +3183,25 @@
       </c>
       <c r="O12" s="159">
         <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P12" s="67">
         <f t="shared" ref="P12:P29" si="5">C$9*F12/100</f>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q12" s="67">
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R12" s="165">
         <f t="shared" si="2"/>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="U12" s="94" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="160" t="s">
         <v>83</v>
       </c>
@@ -3236,53 +3219,50 @@
         <v>7.9</v>
       </c>
       <c r="G13" s="67">
-        <v>144004.50186671762</v>
+        <v>126809.33181271916</v>
       </c>
       <c r="H13" s="159">
         <v>0</v>
       </c>
-      <c r="I13" s="67">
-        <f>144005</f>
-        <v>144005</v>
-      </c>
+      <c r="I13" s="67"/>
       <c r="J13" s="159" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K13" s="159">
         <f t="shared" si="0"/>
-        <v>-0.49813328238087706</v>
+        <v>126809.33181271916</v>
       </c>
       <c r="L13" s="159"/>
       <c r="M13" s="165">
         <f t="shared" si="3"/>
-        <v>-1.4943998471426311E-2</v>
+        <v>3804.2799543815745</v>
       </c>
       <c r="N13" s="165">
         <f t="shared" si="1"/>
-        <v>-0.51307728085230342</v>
+        <v>130613.61176710074</v>
       </c>
       <c r="O13" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P13" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q13" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R13" s="165">
         <f t="shared" si="2"/>
-        <v>126809.33181271916</v>
+        <v>255645.23380710077</v>
       </c>
       <c r="U13" s="94" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="110" t="s">
         <v>84</v>
       </c>
@@ -3298,12 +3278,12 @@
         <v>7.9</v>
       </c>
       <c r="G14" s="158">
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="H14" s="74"/>
       <c r="I14" s="67">
         <f>G14</f>
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="J14" s="65" t="e">
         <f>C8*F14/100</f>
@@ -3324,25 +3304,25 @@
       </c>
       <c r="O14" s="65">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P14" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q14" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R14" s="64">
         <f t="shared" si="2"/>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="U14" s="94" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="110" t="s">
         <v>85</v>
       </c>
@@ -3358,7 +3338,7 @@
         <v>7.9</v>
       </c>
       <c r="G15" s="72">
-        <v>144011.22511827253</v>
+        <v>275141.40676182072</v>
       </c>
       <c r="H15" s="74">
         <v>0</v>
@@ -3370,38 +3350,38 @@
       </c>
       <c r="K15" s="65">
         <f t="shared" si="0"/>
-        <v>144011.22511827253</v>
+        <v>275141.40676182072</v>
       </c>
       <c r="L15" s="65"/>
       <c r="M15" s="64">
         <f t="shared" si="3"/>
-        <v>4320.3367535481757</v>
+        <v>8254.2422028546207</v>
       </c>
       <c r="N15" s="64">
         <f t="shared" si="1"/>
-        <v>148331.56187182071</v>
+        <v>283395.64896467532</v>
       </c>
       <c r="O15" s="65">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P15" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q15" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R15" s="64">
         <f t="shared" si="2"/>
-        <v>275141.40676182072</v>
+        <v>408427.27100467531</v>
       </c>
       <c r="U15" s="94" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="160" t="s">
         <v>86</v>
       </c>
@@ -3412,19 +3392,21 @@
       <c r="D16" s="162" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="163"/>
+      <c r="E16" s="163" t="s">
+        <v>164</v>
+      </c>
       <c r="F16" s="164">
         <v>7.9</v>
       </c>
       <c r="G16" s="67">
-        <v>144011.728561717</v>
+        <v>126809.89046926852</v>
       </c>
       <c r="H16" s="159">
         <v>0</v>
       </c>
       <c r="I16" s="67">
-        <f>154847-I28</f>
-        <v>144011.68431000001</v>
+        <f>136056-I28</f>
+        <v>126810.15472999999</v>
       </c>
       <c r="J16" s="159" t="e">
         <f>C8*F16/100</f>
@@ -3432,38 +3414,38 @@
       </c>
       <c r="K16" s="159">
         <f t="shared" si="0"/>
-        <v>4.4251716986764222E-2</v>
+        <v>-0.26426073147740681</v>
       </c>
       <c r="L16" s="159"/>
       <c r="M16" s="165">
         <f t="shared" si="3"/>
-        <v>1.3275515096029266E-3</v>
+        <v>-7.9278219443222036E-3</v>
       </c>
       <c r="N16" s="165">
         <f t="shared" si="1"/>
-        <v>4.5579268496367148E-2</v>
+        <v>-0.27218855342172898</v>
       </c>
       <c r="O16" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P16" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q16" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R16" s="165">
         <f t="shared" si="2"/>
-        <v>126809.89046926852</v>
+        <v>125031.34985144658</v>
       </c>
       <c r="U16" s="94" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="110" t="s">
         <v>87</v>
       </c>
@@ -3481,14 +3463,14 @@
         <v>7.9</v>
       </c>
       <c r="G17" s="72">
-        <v>152395.81171941914</v>
+        <v>126809.97612170172</v>
       </c>
       <c r="H17" s="65">
         <v>0</v>
       </c>
       <c r="I17" s="67">
-        <f>163231-I23</f>
-        <v>152395.68431000001</v>
+        <f>136056-I23</f>
+        <v>126810.15472999999</v>
       </c>
       <c r="J17" s="65" t="e">
         <f>C8*F17/100</f>
@@ -3496,38 +3478,38 @@
       </c>
       <c r="K17" s="65">
         <f t="shared" si="0"/>
-        <v>0.12740941913216375</v>
+        <v>-0.17860829827259295</v>
       </c>
       <c r="L17" s="65"/>
       <c r="M17" s="64">
         <f t="shared" si="3"/>
-        <v>3.8222825739649123E-3</v>
+        <v>-5.3582489481777884E-3</v>
       </c>
       <c r="N17" s="64">
         <f t="shared" si="1"/>
-        <v>0.13123170170612866</v>
+        <v>-0.18396654722077074</v>
       </c>
       <c r="O17" s="65">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P17" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q17" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R17" s="64">
         <f t="shared" si="2"/>
-        <v>126809.97612170172</v>
+        <v>125031.43807345279</v>
       </c>
       <c r="U17" s="94" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="160" t="s">
         <v>88</v>
       </c>
@@ -3545,50 +3527,53 @@
         <v>7.9</v>
       </c>
       <c r="G18" s="67">
-        <v>466956.0306874633</v>
+        <v>607774.55649808713</v>
       </c>
       <c r="H18" s="159">
         <v>0</v>
       </c>
-      <c r="I18" s="67"/>
+      <c r="I18" s="67">
+        <f>637000-I26</f>
+        <v>607962.16637306078</v>
+      </c>
       <c r="J18" s="159" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K18" s="159">
         <f t="shared" si="0"/>
-        <v>466956.0306874633</v>
+        <v>-187.60987497365568</v>
       </c>
       <c r="L18" s="159"/>
       <c r="M18" s="165">
         <f t="shared" si="3"/>
-        <v>14008.680920623898</v>
+        <v>-5.6282962492096704</v>
       </c>
       <c r="N18" s="165">
         <f t="shared" si="1"/>
-        <v>480964.71160808718</v>
+        <v>-193.23817122286536</v>
       </c>
       <c r="O18" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P18" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q18" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R18" s="165">
         <f t="shared" si="2"/>
-        <v>607774.55649808713</v>
+        <v>124838.38386877713</v>
       </c>
       <c r="U18" s="94" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="160" t="s">
         <v>89</v>
       </c>
@@ -3604,13 +3589,13 @@
         <v>7.9</v>
       </c>
       <c r="G19" s="67">
-        <v>145945.22753571003</v>
+        <v>126697.01361356268</v>
       </c>
       <c r="H19" s="159">
         <v>0</v>
       </c>
       <c r="I19" s="67">
-        <v>146000</v>
+        <v>126700</v>
       </c>
       <c r="J19" s="159" t="e">
         <f>C8*F19/100</f>
@@ -3618,41 +3603,41 @@
       </c>
       <c r="K19" s="159">
         <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
-        <v>-54.77246428997023</v>
+        <v>-2.9863864373182878</v>
       </c>
       <c r="L19" s="159">
         <f>G19-I19</f>
-        <v>-54.77246428997023</v>
+        <v>-2.9863864373182878</v>
       </c>
       <c r="M19" s="165">
         <f t="shared" si="3"/>
-        <v>-3.2863478573982139</v>
+        <v>-0.17918318623909726</v>
       </c>
       <c r="N19" s="165">
         <f t="shared" si="1"/>
-        <v>-112.83127643733867</v>
+        <v>-6.1519560608756727</v>
       </c>
       <c r="O19" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P19" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q19" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R19" s="165">
         <f t="shared" si="2"/>
-        <v>126697.01361356268</v>
+        <v>125025.47008393914</v>
       </c>
       <c r="U19" s="94" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="110" t="s">
         <v>90</v>
       </c>
@@ -3668,12 +3653,12 @@
         <v>7.9</v>
       </c>
       <c r="G20" s="72">
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="H20" s="65"/>
       <c r="I20" s="67">
         <f>G20</f>
-        <v>144011.50634000002</v>
+        <v>126809.84489000001</v>
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="65">
@@ -3691,25 +3676,25 @@
       </c>
       <c r="O20" s="65">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P20" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q20" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R20" s="64">
         <f t="shared" si="2"/>
-        <v>126809.84489000001</v>
+        <v>125031.62204000002</v>
       </c>
       <c r="U20" s="94" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="160" t="s">
         <v>91</v>
       </c>
@@ -3727,48 +3712,48 @@
         <v>7.9</v>
       </c>
       <c r="G21" s="67">
-        <v>266066.69158217852</v>
+        <v>126809.03557658312</v>
       </c>
       <c r="H21" s="159"/>
       <c r="I21" s="67">
-        <f>285283-I24</f>
-        <v>266067.47732335998</v>
+        <f>140000-I24</f>
+        <v>130754.15472999999</v>
       </c>
       <c r="J21" s="159"/>
       <c r="K21" s="159">
         <f t="shared" si="7"/>
-        <v>-0.78574118146207184</v>
+        <v>-3945.1191534168756</v>
       </c>
       <c r="L21" s="159"/>
       <c r="M21" s="165">
         <f t="shared" si="3"/>
-        <v>-2.3572235443862156E-2</v>
+        <v>-118.35357460250627</v>
       </c>
       <c r="N21" s="165">
         <f t="shared" si="8"/>
-        <v>-0.80931341690593395</v>
+        <v>-4063.472728019382</v>
       </c>
       <c r="O21" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P21" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q21" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R21" s="165">
         <f t="shared" si="2"/>
-        <v>126809.03557658312</v>
+        <v>120968.14931198064</v>
       </c>
       <c r="U21" s="94" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="160" t="s">
         <v>92</v>
       </c>
@@ -3786,46 +3771,49 @@
         <v>7.9</v>
       </c>
       <c r="G22" s="67">
-        <v>144011.50634000002</v>
+        <v>275141.69642020005</v>
       </c>
       <c r="H22" s="159"/>
-      <c r="I22" s="67"/>
+      <c r="I22" s="67">
+        <f>295548-I29</f>
+        <v>275141.77956930001</v>
+      </c>
       <c r="J22" s="159"/>
       <c r="K22" s="159">
         <f t="shared" si="7"/>
-        <v>144011.50634000002</v>
+        <v>-8.3149099955335259E-2</v>
       </c>
       <c r="L22" s="159"/>
       <c r="M22" s="165">
         <f t="shared" si="3"/>
-        <v>4320.3451902000006</v>
+        <v>-2.4944729986600576E-3</v>
       </c>
       <c r="N22" s="165">
         <f t="shared" si="8"/>
-        <v>148331.85153020002</v>
+        <v>-8.5643572953995314E-2</v>
       </c>
       <c r="O22" s="159">
         <f t="shared" si="4"/>
-        <v>61551.945450000021</v>
+        <v>75769.282360000012</v>
       </c>
       <c r="P22" s="67">
         <f t="shared" si="5"/>
-        <v>37153.699999999997</v>
+        <v>8690</v>
       </c>
       <c r="Q22" s="67">
         <f t="shared" si="6"/>
-        <v>28104.19944</v>
+        <v>40572.339679999997</v>
       </c>
       <c r="R22" s="165">
         <f t="shared" si="2"/>
-        <v>275141.69642020005</v>
+        <v>125031.53639642705</v>
       </c>
       <c r="S22" s="180"/>
       <c r="U22" s="94" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="110"/>
       <c r="B23" s="71"/>
       <c r="C23" s="94" t="s">
@@ -3842,12 +3830,12 @@
         <v>0.74</v>
       </c>
       <c r="G23" s="72">
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="H23" s="65"/>
       <c r="I23" s="67">
         <f>G23</f>
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65">
@@ -3865,22 +3853,22 @@
       </c>
       <c r="O23" s="65">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P23" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q23" s="65"/>
       <c r="R23" s="64">
         <f t="shared" si="2"/>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U23" s="94" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="160"/>
       <c r="B24" s="161"/>
       <c r="C24" s="95" t="s">
@@ -3897,12 +3885,12 @@
         <v>0.74</v>
       </c>
       <c r="G24" s="67">
-        <v>19215.522676640001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="H24" s="159"/>
       <c r="I24" s="67">
         <f>G24</f>
-        <v>19215.522676640001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="J24" s="159"/>
       <c r="K24" s="159">
@@ -3920,11 +3908,11 @@
       </c>
       <c r="O24" s="159">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P24" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q24" s="159">
         <f>'Calculo Servicios  (2)'!H22</f>
@@ -3932,13 +3920,13 @@
       </c>
       <c r="R24" s="165">
         <f t="shared" si="2"/>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U24" s="94" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="110"/>
       <c r="B25" s="71"/>
       <c r="C25" s="94" t="s">
@@ -3953,12 +3941,12 @@
         <v>0.74</v>
       </c>
       <c r="G25" s="72">
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="H25" s="65"/>
       <c r="I25" s="67">
         <f t="shared" ref="I25" si="9">G25</f>
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="65">
@@ -3976,11 +3964,11 @@
       </c>
       <c r="O25" s="65">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P25" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q25" s="65">
         <f>'Calculo Servicios  (2)'!H23</f>
@@ -3988,13 +3976,13 @@
       </c>
       <c r="R25" s="64">
         <f t="shared" si="2"/>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U25" s="94" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="160"/>
       <c r="B26" s="157"/>
       <c r="C26" s="95" t="s">
@@ -4011,36 +3999,39 @@
         <v>0.74</v>
       </c>
       <c r="G26" s="67">
-        <v>19215.522676640001</v>
+        <v>29037.833626939202</v>
       </c>
       <c r="H26" s="159">
         <v>0</v>
       </c>
-      <c r="I26" s="67"/>
+      <c r="I26" s="67">
+        <f>G26</f>
+        <v>29037.833626939202</v>
+      </c>
       <c r="J26" s="159" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K26" s="159">
         <f t="shared" si="7"/>
-        <v>19215.522676640001</v>
+        <v>0</v>
       </c>
       <c r="L26" s="159"/>
       <c r="M26" s="165">
         <f t="shared" si="3"/>
-        <v>576.46568029920002</v>
+        <v>0</v>
       </c>
       <c r="N26" s="165">
         <f t="shared" si="8"/>
-        <v>19791.9883569392</v>
+        <v>0</v>
       </c>
       <c r="O26" s="159">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P26" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q26" s="159">
         <f>'Calculo Servicios  (2)'!H24</f>
@@ -4048,13 +4039,13 @@
       </c>
       <c r="R26" s="165">
         <f t="shared" si="2"/>
-        <v>29037.833626939202</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U26" s="94" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="110"/>
       <c r="B27" s="71"/>
       <c r="C27" s="94" t="s">
@@ -4069,7 +4060,7 @@
         <v>0.74</v>
       </c>
       <c r="G27" s="72">
-        <v>10835.315690000001</v>
+        <v>20406.220430700003</v>
       </c>
       <c r="H27" s="65">
         <v>0</v>
@@ -4081,24 +4072,24 @@
       </c>
       <c r="K27" s="65">
         <f t="shared" si="7"/>
-        <v>10835.315690000001</v>
+        <v>20406.220430700003</v>
       </c>
       <c r="L27" s="65"/>
       <c r="M27" s="64">
         <f t="shared" si="3"/>
-        <v>325.05947070000002</v>
+        <v>612.18661292100012</v>
       </c>
       <c r="N27" s="64">
         <f t="shared" si="8"/>
-        <v>11160.375160700001</v>
+        <v>21018.407043621002</v>
       </c>
       <c r="O27" s="65">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P27" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q27" s="65">
         <f>'Calculo Servicios  (2)'!H25</f>
@@ -4106,13 +4097,13 @@
       </c>
       <c r="R27" s="64">
         <f t="shared" si="2"/>
-        <v>20406.220430700003</v>
+        <v>28929.782859621002</v>
       </c>
       <c r="U27" s="94" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="184"/>
       <c r="B28" s="185"/>
       <c r="C28" s="95" t="s">
@@ -4122,19 +4113,21 @@
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="163"/>
+      <c r="E28" s="163" t="s">
+        <v>164</v>
+      </c>
       <c r="F28" s="186">
         <v>0.74</v>
       </c>
       <c r="G28" s="67">
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="H28" s="67">
         <v>0</v>
       </c>
       <c r="I28" s="67">
         <f>G28</f>
-        <v>10835.315690000001</v>
+        <v>9245.8452700000016</v>
       </c>
       <c r="J28" s="67">
         <v>0</v>
@@ -4154,11 +4147,11 @@
       </c>
       <c r="O28" s="67">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P28" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q28" s="67">
         <f>'Calculo Servicios  (2)'!H26</f>
@@ -4166,13 +4159,13 @@
       </c>
       <c r="R28" s="179">
         <f t="shared" si="2"/>
-        <v>9245.8452700000016</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U28" s="94" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="160"/>
       <c r="B29" s="173"/>
       <c r="C29" s="95" t="s">
@@ -4189,36 +4182,39 @@
         <v>0.74</v>
       </c>
       <c r="G29" s="67">
-        <v>10835.315690000001</v>
+        <v>20406.220430700003</v>
       </c>
       <c r="H29" s="159">
         <v>0</v>
       </c>
-      <c r="I29" s="67"/>
+      <c r="I29" s="67">
+        <f>G29</f>
+        <v>20406.220430700003</v>
+      </c>
       <c r="J29" s="159" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="K29" s="159">
         <f t="shared" si="7"/>
-        <v>10835.315690000001</v>
+        <v>0</v>
       </c>
       <c r="L29" s="159"/>
       <c r="M29" s="165">
         <f t="shared" si="3"/>
-        <v>325.05947070000002</v>
+        <v>0</v>
       </c>
       <c r="N29" s="165">
         <f t="shared" si="8"/>
-        <v>11160.375160700001</v>
+        <v>0</v>
       </c>
       <c r="O29" s="159">
         <f t="shared" si="4"/>
-        <v>5765.6252700000014</v>
+        <v>7097.3758160000007</v>
       </c>
       <c r="P29" s="67">
         <f t="shared" si="5"/>
-        <v>3480.22</v>
+        <v>814</v>
       </c>
       <c r="Q29" s="159">
         <f>'Calculo Servicios  (2)'!H27</f>
@@ -4226,13 +4222,13 @@
       </c>
       <c r="R29" s="165">
         <f t="shared" si="2"/>
-        <v>20406.220430700003</v>
+        <v>7911.3758160000007</v>
       </c>
       <c r="U29" s="95" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="73"/>
       <c r="B30" s="71"/>
       <c r="C30" s="70"/>
@@ -4260,16 +4256,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="227"/>
-      <c r="B31" s="228"/>
-      <c r="C31" s="228"/>
+    <row r="31" spans="1:21" s="58" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="226"/>
+      <c r="B31" s="227"/>
+      <c r="C31" s="227"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
       <c r="F31" s="97"/>
       <c r="G31" s="61">
         <f>SUM(G11:G30)</f>
-        <v>2276056.3725747587</v>
+        <v>2406065.9424022823</v>
       </c>
       <c r="H31" s="61">
         <f>SUM(H11:H30)</f>
@@ -4277,61 +4273,61 @@
       </c>
       <c r="I31" s="62">
         <f>SUM(I11:I30)</f>
-        <v>1480247.3410500004</v>
+        <v>1987845.22483</v>
       </c>
       <c r="J31" s="61"/>
       <c r="K31" s="62">
         <f>SUM(K11:K30)</f>
-        <v>795809.03152475785</v>
+        <v>418220.71757228236</v>
       </c>
       <c r="L31" s="61"/>
       <c r="M31" s="60"/>
       <c r="N31" s="59"/>
       <c r="O31" s="62">
         <f>SUM(O11:O30)</f>
-        <v>778982.72228999983</v>
+        <v>958913.01903200068</v>
       </c>
       <c r="P31" s="62">
         <f>SUM(P11:P29)</f>
-        <v>470205.93999999989</v>
+        <v>109978</v>
       </c>
       <c r="Q31" s="62">
         <f>SUM(Q11:Q29)</f>
-        <v>337250.39328000002</v>
+        <v>486868.07615999988</v>
       </c>
       <c r="R31" s="62">
         <f>SUM(R11:R29)</f>
-        <v>2406065.9424022823</v>
+        <v>1986523.3583134203</v>
       </c>
       <c r="U31" s="94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="224" t="s">
+    <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="223" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="225"/>
-      <c r="N32" s="225"/>
-      <c r="O32" s="225"/>
-      <c r="P32" s="225"/>
-      <c r="Q32" s="225"/>
-      <c r="R32" s="226"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
+      <c r="M32" s="224"/>
+      <c r="N32" s="224"/>
+      <c r="O32" s="224"/>
+      <c r="P32" s="224"/>
+      <c r="Q32" s="224"/>
+      <c r="R32" s="225"/>
       <c r="U32" s="94" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
       <c r="F33" s="57"/>
       <c r="G33" s="56"/>
       <c r="H33" s="56"/>
@@ -4345,80 +4341,80 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
-      <c r="M34" s="218"/>
-      <c r="N34" s="218"/>
-      <c r="O34" s="218"/>
-    </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C35" s="218"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="218"/>
-      <c r="I35" s="218"/>
-      <c r="J35" s="218"/>
-      <c r="K35" s="218"/>
-      <c r="L35" s="218"/>
-      <c r="M35" s="218"/>
-      <c r="N35" s="218"/>
-      <c r="O35" s="218"/>
-    </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="218"/>
-      <c r="K36" s="218"/>
-      <c r="L36" s="218"/>
-      <c r="M36" s="218"/>
-      <c r="N36" s="218"/>
-      <c r="O36" s="218"/>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="218"/>
-      <c r="D37" s="218"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="218"/>
-      <c r="K37" s="218"/>
-      <c r="L37" s="218"/>
-      <c r="M37" s="218"/>
-      <c r="N37" s="218"/>
-      <c r="O37" s="218"/>
-    </row>
-    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="218"/>
-      <c r="K38" s="218"/>
-      <c r="L38" s="218"/>
-      <c r="M38" s="218"/>
-      <c r="N38" s="218"/>
-      <c r="O38" s="218"/>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C34" s="217"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
+      <c r="J34" s="217"/>
+      <c r="K34" s="217"/>
+      <c r="L34" s="217"/>
+      <c r="M34" s="217"/>
+      <c r="N34" s="217"/>
+      <c r="O34" s="217"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C35" s="217"/>
+      <c r="D35" s="217"/>
+      <c r="E35" s="217"/>
+      <c r="F35" s="217"/>
+      <c r="G35" s="217"/>
+      <c r="H35" s="217"/>
+      <c r="I35" s="217"/>
+      <c r="J35" s="217"/>
+      <c r="K35" s="217"/>
+      <c r="L35" s="217"/>
+      <c r="M35" s="217"/>
+      <c r="N35" s="217"/>
+      <c r="O35" s="217"/>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C36" s="217"/>
+      <c r="D36" s="217"/>
+      <c r="E36" s="217"/>
+      <c r="F36" s="217"/>
+      <c r="G36" s="217"/>
+      <c r="H36" s="217"/>
+      <c r="I36" s="217"/>
+      <c r="J36" s="217"/>
+      <c r="K36" s="217"/>
+      <c r="L36" s="217"/>
+      <c r="M36" s="217"/>
+      <c r="N36" s="217"/>
+      <c r="O36" s="217"/>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="C37" s="217"/>
+      <c r="D37" s="217"/>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
+      <c r="H37" s="217"/>
+      <c r="I37" s="217"/>
+      <c r="J37" s="217"/>
+      <c r="K37" s="217"/>
+      <c r="L37" s="217"/>
+      <c r="M37" s="217"/>
+      <c r="N37" s="217"/>
+      <c r="O37" s="217"/>
+    </row>
+    <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="217"/>
+      <c r="D38" s="217"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
+      <c r="H38" s="217"/>
+      <c r="I38" s="217"/>
+      <c r="J38" s="217"/>
+      <c r="K38" s="217"/>
+      <c r="L38" s="217"/>
+      <c r="M38" s="217"/>
+      <c r="N38" s="217"/>
+      <c r="O38" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4440,31 +4436,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="114" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="114" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.44140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="114" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.42578125" style="114" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="114" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="114"/>
-    <col min="13" max="13" width="14.6640625" style="114" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5546875" style="114" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="114"/>
+    <col min="9" max="12" width="11.42578125" style="114"/>
+    <col min="13" max="13" width="14.7109375" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="114" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="231" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="233"/>
-    </row>
-    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="232"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="155"/>
       <c r="B2" s="140"/>
       <c r="C2" s="140"/>
@@ -4473,7 +4469,7 @@
       </c>
       <c r="E2" s="151"/>
     </row>
-    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="153">
         <f>13+28+19</f>
         <v>60</v>
@@ -4495,38 +4491,38 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="150"/>
       <c r="B4" s="149"/>
       <c r="C4" s="149"/>
       <c r="D4" s="149"/>
       <c r="E4" s="148"/>
     </row>
-    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="147"/>
       <c r="B5" s="147"/>
       <c r="C5" s="147"/>
       <c r="D5" s="147"/>
       <c r="E5" s="147"/>
     </row>
-    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="147"/>
       <c r="B6" s="147"/>
       <c r="C6" s="147"/>
       <c r="D6" s="147"/>
       <c r="E6" s="147"/>
     </row>
-    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="234" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="233" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="235"/>
-      <c r="C7" s="235"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="236"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="234"/>
+      <c r="H7" s="235"/>
       <c r="L7" s="114" t="s">
         <v>72</v>
       </c>
@@ -4534,7 +4530,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="107">
         <v>400523.88</v>
       </c>
@@ -4570,7 +4566,7 @@
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="143" t="s">
         <v>34</v>
       </c>
@@ -4619,7 +4615,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="141" t="s">
         <v>35</v>
       </c>
@@ -4668,7 +4664,7 @@
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="141" t="s">
         <v>36</v>
       </c>
@@ -4716,7 +4712,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="141" t="s">
         <v>37</v>
       </c>
@@ -4763,7 +4759,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="141" t="s">
         <v>38</v>
       </c>
@@ -4806,7 +4802,7 @@
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="141" t="s">
         <v>39</v>
       </c>
@@ -4841,7 +4837,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="141" t="s">
         <v>40</v>
       </c>
@@ -4880,7 +4876,7 @@
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="141" t="s">
         <v>41</v>
       </c>
@@ -4915,7 +4911,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="141" t="s">
         <v>42</v>
       </c>
@@ -4950,7 +4946,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="141" t="s">
         <v>43</v>
       </c>
@@ -4985,7 +4981,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
         <v>44</v>
       </c>
@@ -5020,7 +5016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="141" t="s">
         <v>45</v>
       </c>
@@ -5052,7 +5048,7 @@
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="139" t="s">
         <v>139</v>
       </c>
@@ -5074,7 +5070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="100">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
@@ -5084,7 +5080,7 @@
       </c>
       <c r="L22" s="134"/>
     </row>
-    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="99">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
@@ -5093,35 +5089,35 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="132"/>
       <c r="J25" s="114">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="J26" s="114">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J27" s="114">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="237" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="236" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="238"/>
-      <c r="D28" s="238"/>
-      <c r="E28" s="238"/>
-      <c r="F28" s="239"/>
+      <c r="C28" s="237"/>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
       <c r="J28" s="114">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="131" t="s">
         <v>137</v>
       </c>
@@ -5141,7 +5137,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="125" t="s">
         <v>132</v>
       </c>
@@ -5164,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="125" t="s">
         <v>131</v>
       </c>
@@ -5183,7 +5179,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="125" t="s">
         <v>130</v>
       </c>
@@ -5202,7 +5198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="125" t="s">
         <v>129</v>
       </c>
@@ -5225,7 +5221,7 @@
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="125" t="s">
         <v>128</v>
       </c>
@@ -5244,7 +5240,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="125" t="s">
         <v>127</v>
       </c>
@@ -5263,7 +5259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="125" t="s">
         <v>126</v>
       </c>
@@ -5282,7 +5278,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="125" t="s">
         <v>125</v>
       </c>
@@ -5298,7 +5294,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="125" t="s">
         <v>124</v>
       </c>
@@ -5320,7 +5316,7 @@
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="125" t="s">
         <v>122</v>
       </c>
@@ -5334,7 +5330,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="125" t="s">
         <v>121</v>
       </c>
@@ -5348,7 +5344,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="125" t="s">
         <v>120</v>
       </c>
@@ -5362,7 +5358,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="125" t="s">
         <v>119</v>
       </c>
@@ -5376,7 +5372,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="125" t="s">
         <v>118</v>
       </c>
@@ -5390,7 +5386,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="122" t="s">
         <v>117</v>
       </c>
@@ -5404,7 +5400,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="122" t="s">
         <v>116</v>
       </c>
@@ -5418,7 +5414,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="122" t="s">
         <v>115</v>
       </c>
@@ -5432,7 +5428,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="118" t="s">
         <v>114</v>
       </c>
